--- a/et_custom_input_data.xlsx
+++ b/et_custom_input_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\eagar-tsai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\ETtoKGT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1913D08-7761-41EE-80A7-711546AF6286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACB2895-257D-4B24-87B8-0AA76F425200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="10932" xr2:uid="{D50FBC2E-9E0F-4B27-B5AE-2B4706E55574}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D50FBC2E-9E0F-4B27-B5AE-2B4706E55574}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="160">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -507,6 +507,18 @@
   </si>
   <si>
     <t>0 (TC)</t>
+  </si>
+  <si>
+    <t>Ni95Nb5 (TC)</t>
+  </si>
+  <si>
+    <t>(was 0.51)</t>
+  </si>
+  <si>
+    <t>Mo2Ta58W40</t>
+  </si>
+  <si>
+    <t>W40Ta57Mo2</t>
   </si>
 </sst>
 </file>
@@ -525,14 +537,21 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF9B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -562,18 +581,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF9B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -902,8 +930,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7095CECD-B3C1-479B-A395-9B195FCE92D6}">
-  <dimension ref="A1:ES5"/>
+  <dimension ref="A1:ES8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="20" max="20" width="8.88671875" style="4"/>
+    <col min="23" max="24" width="8.88671875" style="4"/>
+    <col min="78" max="78" width="8.88671875" style="4"/>
+    <col min="89" max="89" width="8.88671875" style="4"/>
+    <col min="141" max="141" width="8.88671875" style="4"/>
+    <col min="143" max="143" width="8.88671875" style="4"/>
+    <col min="146" max="146" width="8.88671875" style="4"/>
+    <col min="148" max="148" width="8.88671875" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:149" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -963,7 +1001,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -972,10 +1010,10 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
@@ -1137,7 +1175,7 @@
       <c r="BY1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>77</v>
       </c>
       <c r="CA1" s="1" t="s">
@@ -1170,7 +1208,7 @@
       <c r="CJ1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" s="3" t="s">
         <v>88</v>
       </c>
       <c r="CL1" s="1" t="s">
@@ -1326,13 +1364,13 @@
       <c r="EJ1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="EK1" s="1" t="s">
+      <c r="EK1" s="3" t="s">
         <v>140</v>
       </c>
       <c r="EL1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="EM1" s="1" t="s">
+      <c r="EM1" s="3" t="s">
         <v>142</v>
       </c>
       <c r="EN1" s="1" t="s">
@@ -1341,13 +1379,13 @@
       <c r="EO1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="EP1" s="1" t="s">
+      <c r="EP1" s="3" t="s">
         <v>145</v>
       </c>
       <c r="EQ1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="ER1" s="1" t="s">
+      <c r="ER1" s="3" t="s">
         <v>147</v>
       </c>
       <c r="ES1" s="1" t="s">
@@ -1412,7 +1450,7 @@
       <c r="S2">
         <v>180.586792</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="4">
         <v>0.59024308526460278</v>
       </c>
       <c r="U2">
@@ -1421,10 +1459,10 @@
       <c r="V2">
         <v>500</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="4">
         <v>250</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="4">
         <v>0.5</v>
       </c>
       <c r="Y2">
@@ -1586,7 +1624,7 @@
       <c r="BY2">
         <v>223.4316130129728</v>
       </c>
-      <c r="BZ2">
+      <c r="BZ2" s="4">
         <v>3454.8464667112039</v>
       </c>
       <c r="CA2">
@@ -1619,7 +1657,7 @@
       <c r="CJ2">
         <v>45.438765082508333</v>
       </c>
-      <c r="CK2">
+      <c r="CK2" s="4">
         <v>23.749503542473981</v>
       </c>
       <c r="CL2">
@@ -1775,14 +1813,14 @@
       <c r="EJ2">
         <v>47.055460931158187</v>
       </c>
-      <c r="EK2">
+      <c r="EK2" s="4">
         <v>260.56978148854978</v>
       </c>
       <c r="EL2">
         <v>256.22807750030222</v>
       </c>
-      <c r="EM2">
-        <v>18038.920722240109</v>
+      <c r="EM2" s="4">
+        <v>18038.920722240098</v>
       </c>
       <c r="EN2">
         <v>16462.475431757292</v>
@@ -1790,14 +1828,14 @@
       <c r="EO2">
         <v>15296.24612336383</v>
       </c>
-      <c r="EP2">
+      <c r="EP2" s="4">
         <v>7.9999999999999993E-5</v>
       </c>
       <c r="EQ2" t="s">
         <v>151</v>
       </c>
-      <c r="ER2">
-        <v>251.61732250334421</v>
+      <c r="ER2" s="4">
+        <v>251.61732250334401</v>
       </c>
       <c r="ES2">
         <v>136.9653877916283</v>
@@ -1810,28 +1848,31 @@
       <c r="B3" t="s">
         <v>153</v>
       </c>
-      <c r="T3">
-        <v>0.51</v>
-      </c>
-      <c r="W3">
+      <c r="T3" s="4">
+        <v>0.501</v>
+      </c>
+      <c r="U3" t="s">
+        <v>157</v>
+      </c>
+      <c r="W3" s="4">
         <v>250</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="4">
         <v>0.5</v>
       </c>
-      <c r="BZ3">
+      <c r="BZ3" s="4">
         <v>1703</v>
       </c>
-      <c r="CK3">
+      <c r="CK3" s="4">
         <v>70.400000000000006</v>
       </c>
-      <c r="EM3">
+      <c r="EM3" s="4">
         <v>8909</v>
       </c>
-      <c r="EP3">
-        <v>7.9999999999999993E-5</v>
-      </c>
-      <c r="ER3">
+      <c r="EP3" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="ER3" s="4">
         <v>636.19000000000005</v>
       </c>
     </row>
@@ -1893,7 +1934,7 @@
       <c r="S4">
         <v>180.586792</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="4">
         <v>0.59024308526460278</v>
       </c>
       <c r="U4">
@@ -1902,10 +1943,10 @@
       <c r="V4">
         <v>500</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="4">
         <v>250</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="4">
         <v>0.5</v>
       </c>
       <c r="Y4">
@@ -2067,7 +2108,7 @@
       <c r="BY4">
         <v>223.4316130129728</v>
       </c>
-      <c r="BZ4">
+      <c r="BZ4" s="4">
         <v>3454.8464667112039</v>
       </c>
       <c r="CA4">
@@ -2100,7 +2141,7 @@
       <c r="CJ4">
         <v>45.438765082508333</v>
       </c>
-      <c r="CK4">
+      <c r="CK4" s="4">
         <v>23.749503542473981</v>
       </c>
       <c r="CL4">
@@ -2256,13 +2297,13 @@
       <c r="EJ4">
         <v>47.055460931158187</v>
       </c>
-      <c r="EK4">
+      <c r="EK4" s="4">
         <v>260.56978148854978</v>
       </c>
       <c r="EL4">
         <v>256.22807750030222</v>
       </c>
-      <c r="EM4">
+      <c r="EM4" s="4">
         <v>18038.920722240109</v>
       </c>
       <c r="EN4">
@@ -2271,13 +2312,13 @@
       <c r="EO4">
         <v>15296.24612336383</v>
       </c>
-      <c r="EP4">
+      <c r="EP4" s="4">
         <v>7.9999999999999993E-5</v>
       </c>
       <c r="EQ4" t="s">
         <v>151</v>
       </c>
-      <c r="ER4">
+      <c r="ER4" s="4">
         <v>2084.7584814613701</v>
       </c>
       <c r="ES4">
@@ -2342,7 +2383,7 @@
       <c r="S5">
         <v>180.586792</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="4">
         <v>0.590243085</v>
       </c>
       <c r="U5">
@@ -2351,10 +2392,10 @@
       <c r="V5">
         <v>500</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="4">
         <v>250</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="4">
         <v>0.5</v>
       </c>
       <c r="Y5">
@@ -2516,7 +2557,7 @@
       <c r="BY5">
         <v>223.431613</v>
       </c>
-      <c r="BZ5">
+      <c r="BZ5" s="4">
         <v>3454.8464669999998</v>
       </c>
       <c r="CA5">
@@ -2549,7 +2590,7 @@
       <c r="CJ5">
         <v>45.438765080000003</v>
       </c>
-      <c r="CK5">
+      <c r="CK5" s="4">
         <v>23.749503539999999</v>
       </c>
       <c r="CL5">
@@ -2705,13 +2746,13 @@
       <c r="EJ5">
         <v>47.055460930000002</v>
       </c>
-      <c r="EK5">
+      <c r="EK5" s="4">
         <v>260.56978149999998</v>
       </c>
       <c r="EL5">
         <v>256.22807749999998</v>
       </c>
-      <c r="EM5">
+      <c r="EM5" s="4">
         <v>18038.920719999998</v>
       </c>
       <c r="EN5">
@@ -2720,16 +2761,961 @@
       <c r="EO5">
         <v>15296.24612</v>
       </c>
-      <c r="EP5">
+      <c r="EP5" s="4">
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="EQ5" t="s">
         <v>151</v>
       </c>
-      <c r="ER5">
+      <c r="ER5" s="4">
         <v>501.56474108170266</v>
       </c>
       <c r="ES5">
+        <v>136.9653878</v>
+      </c>
+    </row>
+    <row r="6" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" t="s">
+        <v>153</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0.501</v>
+      </c>
+      <c r="W6" s="4">
+        <v>250</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="BZ6" s="4">
+        <v>1705.11904</v>
+      </c>
+      <c r="CA6">
+        <v>1691.2912100000001</v>
+      </c>
+      <c r="CK6" s="4">
+        <v>45.700569999999999</v>
+      </c>
+      <c r="EK6" s="4">
+        <v>740.57488219333595</v>
+      </c>
+      <c r="EL6">
+        <v>639.93263999999999</v>
+      </c>
+      <c r="EM6" s="4">
+        <v>8894.8914399999994</v>
+      </c>
+      <c r="EN6">
+        <v>8285.9647600000008</v>
+      </c>
+      <c r="EO6">
+        <v>7847.1017000000002</v>
+      </c>
+      <c r="EP6" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="ER6" s="4">
+        <v>705.89381000000003</v>
+      </c>
+      <c r="ES6">
+        <v>437.98635000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7">
+        <v>0.4</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G7">
+        <v>0.02</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>3452.4276749999999</v>
+      </c>
+      <c r="L7">
+        <v>15182.13689</v>
+      </c>
+      <c r="M7">
+        <v>19395.954269999998</v>
+      </c>
+      <c r="N7">
+        <v>23.466295039999999</v>
+      </c>
+      <c r="O7">
+        <v>11.797217359999999</v>
+      </c>
+      <c r="P7">
+        <v>4.42E-6</v>
+      </c>
+      <c r="Q7">
+        <v>6.2299999999999996E-6</v>
+      </c>
+      <c r="R7">
+        <v>248.2626156</v>
+      </c>
+      <c r="S7">
+        <v>180.404582</v>
+      </c>
+      <c r="T7">
+        <v>0.5662496311375983</v>
+      </c>
+      <c r="U7">
+        <v>250</v>
+      </c>
+      <c r="V7">
+        <v>500</v>
+      </c>
+      <c r="W7">
+        <v>250</v>
+      </c>
+      <c r="X7">
+        <v>0.5</v>
+      </c>
+      <c r="Y7">
+        <v>500</v>
+      </c>
+      <c r="Z7">
+        <v>117.892</v>
+      </c>
+      <c r="AA7">
+        <v>5.4620000000000024</v>
+      </c>
+      <c r="AB7">
+        <v>69.010000000000005</v>
+      </c>
+      <c r="AC7">
+        <v>0.54141968100000004</v>
+      </c>
+      <c r="AD7">
+        <v>3.4289049999999999E-3</v>
+      </c>
+      <c r="AF7">
+        <v>132</v>
+      </c>
+      <c r="AG7">
+        <v>32</v>
+      </c>
+      <c r="AH7">
+        <v>2000</v>
+      </c>
+      <c r="AI7">
+        <v>16.925799999999999</v>
+      </c>
+      <c r="AJ7">
+        <v>180.40600000000001</v>
+      </c>
+      <c r="AK7">
+        <v>3444.12</v>
+      </c>
+      <c r="AL7">
+        <v>5.42</v>
+      </c>
+      <c r="AM7">
+        <v>2.3752257132538821</v>
+      </c>
+      <c r="AN7">
+        <v>0.31540000000000001</v>
+      </c>
+      <c r="AO7">
+        <v>244.6</v>
+      </c>
+      <c r="AP7">
+        <v>102.979686787289</v>
+      </c>
+      <c r="AQ7">
+        <v>270.91896000000003</v>
+      </c>
+      <c r="AR7">
+        <v>103.66</v>
+      </c>
+      <c r="AS7">
+        <v>367.76199999999977</v>
+      </c>
+      <c r="AT7">
+        <v>179.8</v>
+      </c>
+      <c r="AU7">
+        <v>98.581999999999994</v>
+      </c>
+      <c r="AV7">
+        <v>81.218000000000004</v>
+      </c>
+      <c r="AW7">
+        <v>1.0489567040146419</v>
+      </c>
+      <c r="AX7">
+        <v>2.7418773630646671E-3</v>
+      </c>
+      <c r="AY7">
+        <v>242.45400000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>98.581999999999994</v>
+      </c>
+      <c r="BA7">
+        <v>1.8572</v>
+      </c>
+      <c r="BB7">
+        <v>144.20599999999999</v>
+      </c>
+      <c r="BC7">
+        <v>0.76069851461439475</v>
+      </c>
+      <c r="BD7">
+        <v>2.8524565613155889E-2</v>
+      </c>
+      <c r="BE7">
+        <v>5.0331231812407971E-3</v>
+      </c>
+      <c r="BF7">
+        <v>0.11398878982725839</v>
+      </c>
+      <c r="BG7">
+        <v>2.0612884455182881E-4</v>
+      </c>
+      <c r="BH7">
+        <v>4.600789181995979E-2</v>
+      </c>
+      <c r="BI7">
+        <v>0.45908771529520931</v>
+      </c>
+      <c r="BJ7">
+        <v>2.0338102463182128E-2</v>
+      </c>
+      <c r="BK7">
+        <v>9.2591707218551395E-2</v>
+      </c>
+      <c r="BL7">
+        <v>0.21897609720168579</v>
+      </c>
+      <c r="BM7">
+        <v>1431.936015036094</v>
+      </c>
+      <c r="BN7">
+        <v>0.35402229140711838</v>
+      </c>
+      <c r="BO7">
+        <v>2.3817671346009321</v>
+      </c>
+      <c r="BP7">
+        <v>3.3776309888147373E-2</v>
+      </c>
+      <c r="BQ7">
+        <v>1021.667756163867</v>
+      </c>
+      <c r="BR7">
+        <v>462.5321982758847</v>
+      </c>
+      <c r="BS7">
+        <v>733.71631051300199</v>
+      </c>
+      <c r="BT7">
+        <v>374.44671474854761</v>
+      </c>
+      <c r="BU7">
+        <v>101.3289296644421</v>
+      </c>
+      <c r="BV7">
+        <v>180.9969194446137</v>
+      </c>
+      <c r="BW7">
+        <v>4.3729126804472121E-2</v>
+      </c>
+      <c r="BX7">
+        <v>131.18738041341641</v>
+      </c>
+      <c r="BY7">
+        <v>190.13073735497599</v>
+      </c>
+      <c r="BZ7">
+        <v>3452.427675333764</v>
+      </c>
+      <c r="CA7">
+        <v>3428.0342888596838</v>
+      </c>
+      <c r="CB7">
+        <v>16.311856606373631</v>
+      </c>
+      <c r="CC7">
+        <v>47.293311610701487</v>
+      </c>
+      <c r="CD7">
+        <v>50.626010270000442</v>
+      </c>
+      <c r="CE7">
+        <v>1.9752692236002092E-2</v>
+      </c>
+      <c r="CF7">
+        <v>1.1839427634254791E-5</v>
+      </c>
+      <c r="CG7">
+        <v>1.1317877165521829E-6</v>
+      </c>
+      <c r="CH7">
+        <v>883557.91936525505</v>
+      </c>
+      <c r="CI7">
+        <v>15.182136894859971</v>
+      </c>
+      <c r="CJ7">
+        <v>44.787713268306099</v>
+      </c>
+      <c r="CK7">
+        <v>23.466295036133062</v>
+      </c>
+      <c r="CL7">
+        <v>4.261431122638723E-2</v>
+      </c>
+      <c r="CM7">
+        <v>6.2260536610449757E-6</v>
+      </c>
+      <c r="CN7">
+        <v>2.5752174884361701E-6</v>
+      </c>
+      <c r="CO7">
+        <v>388316.71673962619</v>
+      </c>
+      <c r="CP7">
+        <v>17.52569393987282</v>
+      </c>
+      <c r="CQ7">
+        <v>24.81833698220726</v>
+      </c>
+      <c r="CR7">
+        <v>53.103861434433448</v>
+      </c>
+      <c r="CS7">
+        <v>1.8831022320941481E-2</v>
+      </c>
+      <c r="CT7">
+        <v>2.202613652002335E-5</v>
+      </c>
+      <c r="CU7">
+        <v>9.6505257108005921E-8</v>
+      </c>
+      <c r="CV7">
+        <v>10362129.794450769</v>
+      </c>
+      <c r="CW7">
+        <v>16.837176607644029</v>
+      </c>
+      <c r="CX7">
+        <v>33.224163184058852</v>
+      </c>
+      <c r="CY7">
+        <v>50.721921764789798</v>
+      </c>
+      <c r="CZ7">
+        <v>1.971534132001641E-2</v>
+      </c>
+      <c r="DA7">
+        <v>1.6358086727621499E-5</v>
+      </c>
+      <c r="DB7">
+        <v>7.695914793153597E-7</v>
+      </c>
+      <c r="DC7">
+        <v>1299390.6856786089</v>
+      </c>
+      <c r="DD7">
+        <v>-7076.4899264596033</v>
+      </c>
+      <c r="DE7">
+        <v>-7076.4899269644366</v>
+      </c>
+      <c r="DF7">
+        <v>53.103861434433462</v>
+      </c>
+      <c r="DG7">
+        <v>17.52569393987282</v>
+      </c>
+      <c r="DH7">
+        <v>180.40979999999999</v>
+      </c>
+      <c r="DI7">
+        <v>1.0294017493341501E-5</v>
+      </c>
+      <c r="DJ7">
+        <v>1</v>
+      </c>
+      <c r="DK7">
+        <v>1</v>
+      </c>
+      <c r="DL7">
+        <v>49705.909397774412</v>
+      </c>
+      <c r="DM7">
+        <v>49705.909397774412</v>
+      </c>
+      <c r="DN7">
+        <v>50.721921764789784</v>
+      </c>
+      <c r="DO7">
+        <v>16.837176607644039</v>
+      </c>
+      <c r="DP7">
+        <v>180.40979999999999</v>
+      </c>
+      <c r="DQ7">
+        <v>1.071496749152672E-5</v>
+      </c>
+      <c r="DR7">
+        <v>1</v>
+      </c>
+      <c r="DS7">
+        <v>1</v>
+      </c>
+      <c r="DT7">
+        <v>95054.209601043636</v>
+      </c>
+      <c r="DU7">
+        <v>95054.209601043593</v>
+      </c>
+      <c r="DV7">
+        <v>50.626245819296038</v>
+      </c>
+      <c r="DW7">
+        <v>16.312361877372741</v>
+      </c>
+      <c r="DX7">
+        <v>180.40979999999999</v>
+      </c>
+      <c r="DY7">
+        <v>1.1059698243345771E-5</v>
+      </c>
+      <c r="DZ7">
+        <v>1</v>
+      </c>
+      <c r="EA7">
+        <v>1</v>
+      </c>
+      <c r="EB7">
+        <v>139015.94454453461</v>
+      </c>
+      <c r="EC7">
+        <v>139015.94454453461</v>
+      </c>
+      <c r="ED7">
+        <v>23.466946175797549</v>
+      </c>
+      <c r="EE7">
+        <v>9.1467814257122082E-3</v>
+      </c>
+      <c r="EF7">
+        <v>6.0251674549038424E-7</v>
+      </c>
+      <c r="EG7">
+        <v>15.180958030083801</v>
+      </c>
+      <c r="EH7">
+        <v>1.188395354512445E-5</v>
+      </c>
+      <c r="EI7">
+        <v>2.249174285049091</v>
+      </c>
+      <c r="EJ7">
+        <v>46.313451918355128</v>
+      </c>
+      <c r="EK7">
+        <v>256.71993141701432</v>
+      </c>
+      <c r="EL7">
+        <v>262.15138820976</v>
+      </c>
+      <c r="EM7">
+        <v>17525.693939872821</v>
+      </c>
+      <c r="EN7">
+        <v>16311.856606373631</v>
+      </c>
+      <c r="EO7">
+        <v>15182.13689485997</v>
+      </c>
+      <c r="EP7">
+        <v>7.9999999999999993E-5</v>
+      </c>
+      <c r="EQ7" t="s">
+        <v>159</v>
+      </c>
+      <c r="ER7">
+        <v>248.26261490579051</v>
+      </c>
+      <c r="ES7">
+        <v>137.57043588952331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8">
+        <v>0.48</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.48</v>
+      </c>
+      <c r="G8">
+        <v>0.02</v>
+      </c>
+      <c r="H8">
+        <v>0.02</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="L8">
+        <v>15296.24612</v>
+      </c>
+      <c r="M8">
+        <v>19370.285759999999</v>
+      </c>
+      <c r="N8">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="O8">
+        <v>10.71769387</v>
+      </c>
+      <c r="P8">
+        <v>4.0400000000000003E-6</v>
+      </c>
+      <c r="Q8">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="R8">
+        <v>251.61732309999999</v>
+      </c>
+      <c r="S8">
+        <v>180.586792</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0.590243085</v>
+      </c>
+      <c r="U8">
+        <v>250</v>
+      </c>
+      <c r="V8">
+        <v>500</v>
+      </c>
+      <c r="W8" s="4">
+        <v>125</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y8">
+        <v>500</v>
+      </c>
+      <c r="Z8">
+        <v>114.596</v>
+      </c>
+      <c r="AA8">
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AB8">
+        <v>96.084999999999994</v>
+      </c>
+      <c r="AC8">
+        <v>0.45542277199999998</v>
+      </c>
+      <c r="AD8">
+        <v>2.9943729999999998E-3</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF8">
+        <v>164</v>
+      </c>
+      <c r="AG8">
+        <v>52</v>
+      </c>
+      <c r="AH8">
+        <v>2000</v>
+      </c>
+      <c r="AI8">
+        <v>16.931000000000001</v>
+      </c>
+      <c r="AJ8">
+        <v>180.58799999999999</v>
+      </c>
+      <c r="AK8">
+        <v>3460.84</v>
+      </c>
+      <c r="AL8">
+        <v>5.48</v>
+      </c>
+      <c r="AM8">
+        <v>2.3149717509999999</v>
+      </c>
+      <c r="AN8">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="AO8">
+        <v>251.6</v>
+      </c>
+      <c r="AP8">
+        <v>108.6838316</v>
+      </c>
+      <c r="AQ8">
+        <v>285.01247999999998</v>
+      </c>
+      <c r="AR8">
+        <v>110.44</v>
+      </c>
+      <c r="AS8">
+        <v>384.57</v>
+      </c>
+      <c r="AT8">
+        <v>181.756</v>
+      </c>
+      <c r="AU8">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="AV8">
+        <v>78.028000000000006</v>
+      </c>
+      <c r="AW8">
+        <v>1.0228879660000001</v>
+      </c>
+      <c r="AX8">
+        <v>6.1456499999999997E-4</v>
+      </c>
+      <c r="AY8">
+        <v>249.3606667</v>
+      </c>
+      <c r="AZ8">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="BA8">
+        <v>1.9219999999999999</v>
+      </c>
+      <c r="BB8">
+        <v>143.96</v>
+      </c>
+      <c r="BC8">
+        <v>0.86109132799999999</v>
+      </c>
+      <c r="BD8">
+        <v>2.5713613999999999E-2</v>
+      </c>
+      <c r="BE8">
+        <v>4.8244129999999996E-3</v>
+      </c>
+      <c r="BF8">
+        <v>0.100737432</v>
+      </c>
+      <c r="BG8">
+        <v>2.1614299999999999E-4</v>
+      </c>
+      <c r="BH8">
+        <v>5.2086074000000003E-2</v>
+      </c>
+      <c r="BI8">
+        <v>0.453460048</v>
+      </c>
+      <c r="BJ8">
+        <v>2.4708790000000001E-2</v>
+      </c>
+      <c r="BK8">
+        <v>9.8234493000000006E-2</v>
+      </c>
+      <c r="BL8">
+        <v>0.22919963500000001</v>
+      </c>
+      <c r="BM8">
+        <v>1453.6841870000001</v>
+      </c>
+      <c r="BN8">
+        <v>0.476258615</v>
+      </c>
+      <c r="BO8">
+        <v>2.8367983109999999</v>
+      </c>
+      <c r="BP8">
+        <v>6.4197078000000005E-2</v>
+      </c>
+      <c r="BQ8">
+        <v>1382.2900990000001</v>
+      </c>
+      <c r="BR8">
+        <v>572.84799610000005</v>
+      </c>
+      <c r="BS8">
+        <v>1042.2361960000001</v>
+      </c>
+      <c r="BT8">
+        <v>468.82416499999999</v>
+      </c>
+      <c r="BU8">
+        <v>192.5912342</v>
+      </c>
+      <c r="BV8">
+        <v>208.91441850000001</v>
+      </c>
+      <c r="BW8">
+        <v>8.0015981E-2</v>
+      </c>
+      <c r="BX8">
+        <v>240.04794290000001</v>
+      </c>
+      <c r="BY8">
+        <v>223.431613</v>
+      </c>
+      <c r="BZ8" s="4">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="CA8">
+        <v>3358.7692830000001</v>
+      </c>
+      <c r="CB8">
+        <v>16.462475430000001</v>
+      </c>
+      <c r="CC8">
+        <v>46.271406540000001</v>
+      </c>
+      <c r="CD8">
+        <v>45.715451539999997</v>
+      </c>
+      <c r="CE8">
+        <v>2.1874442000000001E-2</v>
+      </c>
+      <c r="CF8" s="2">
+        <v>1.08381E-5</v>
+      </c>
+      <c r="CG8" s="2">
+        <v>1.10306E-6</v>
+      </c>
+      <c r="CH8">
+        <v>906572.58589999995</v>
+      </c>
+      <c r="CI8">
+        <v>15.296246119999999</v>
+      </c>
+      <c r="CJ8">
+        <v>45.438765080000003</v>
+      </c>
+      <c r="CK8" s="4">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="CL8">
+        <v>4.2106142999999999E-2</v>
+      </c>
+      <c r="CM8" s="2">
+        <v>6.17082E-6</v>
+      </c>
+      <c r="CN8" s="2">
+        <v>2.7980799999999998E-6</v>
+      </c>
+      <c r="CO8">
+        <v>357388.13919999998</v>
+      </c>
+      <c r="CP8">
+        <v>18.03892072</v>
+      </c>
+      <c r="CQ8">
+        <v>24.73414</v>
+      </c>
+      <c r="CR8">
+        <v>48.265258959999997</v>
+      </c>
+      <c r="CS8">
+        <v>2.0718836000000001E-2</v>
+      </c>
+      <c r="CT8" s="2">
+        <v>1.95356E-5</v>
+      </c>
+      <c r="CU8" s="2">
+        <v>3.2153999999999999E-9</v>
+      </c>
+      <c r="CV8">
+        <v>311003330.30000001</v>
+      </c>
+      <c r="CW8">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="CX8">
+        <v>33.403267239999998</v>
+      </c>
+      <c r="CY8">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="CZ8">
+        <v>2.1731309000000001E-2</v>
+      </c>
+      <c r="DA8" s="2">
+        <v>1.46722E-5</v>
+      </c>
+      <c r="DB8" s="2">
+        <v>7.5787200000000005E-7</v>
+      </c>
+      <c r="DC8">
+        <v>1319484.453</v>
+      </c>
+      <c r="DD8">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DE8">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DF8">
+        <v>49.317869760000001</v>
+      </c>
+      <c r="DG8">
+        <v>18.03892072</v>
+      </c>
+      <c r="DH8">
+        <v>180.5926</v>
+      </c>
+      <c r="DI8" s="2">
+        <v>1.00113E-5</v>
+      </c>
+      <c r="DJ8">
+        <v>0.94</v>
+      </c>
+      <c r="DK8">
+        <v>0.94</v>
+      </c>
+      <c r="DL8">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DM8">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DN8">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="DO8">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="DP8">
+        <v>180.5926</v>
+      </c>
+      <c r="DQ8" s="2">
+        <v>1.0650500000000001E-5</v>
+      </c>
+      <c r="DR8">
+        <v>1</v>
+      </c>
+      <c r="DS8">
+        <v>1</v>
+      </c>
+      <c r="DT8">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DU8">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DV8">
+        <v>45.715752180000003</v>
+      </c>
+      <c r="DW8">
+        <v>16.462982400000001</v>
+      </c>
+      <c r="DX8">
+        <v>180.5926</v>
+      </c>
+      <c r="DY8" s="2">
+        <v>1.0969600000000001E-5</v>
+      </c>
+      <c r="DZ8">
+        <v>1</v>
+      </c>
+      <c r="EA8">
+        <v>1</v>
+      </c>
+      <c r="EB8">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="EC8">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="ED8">
+        <v>23.75028618</v>
+      </c>
+      <c r="EE8">
+        <v>9.2622520000000003E-3</v>
+      </c>
+      <c r="EF8" s="2">
+        <v>6.0556999999999999E-7</v>
+      </c>
+      <c r="EG8">
+        <v>15.295102</v>
+      </c>
+      <c r="EH8" s="2">
+        <v>1.1807199999999999E-5</v>
+      </c>
+      <c r="EI8">
+        <v>2.253734219</v>
+      </c>
+      <c r="EJ8">
+        <v>47.055460930000002</v>
+      </c>
+      <c r="EK8" s="4">
+        <v>260.56978149999998</v>
+      </c>
+      <c r="EL8">
+        <v>256.22807749999998</v>
+      </c>
+      <c r="EM8" s="4">
+        <v>18038.920719999998</v>
+      </c>
+      <c r="EN8">
+        <v>16462.475429999999</v>
+      </c>
+      <c r="EO8">
+        <v>15296.24612</v>
+      </c>
+      <c r="EP8" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="EQ8" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER8" s="4">
+        <v>251.6173225</v>
+      </c>
+      <c r="ES8">
         <v>136.9653878</v>
       </c>
     </row>

--- a/et_custom_input_data.xlsx
+++ b/et_custom_input_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\ETtoKGT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACB2895-257D-4B24-87B8-0AA76F425200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B474354C-AF7A-4285-A46A-6BD9654C5A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D50FBC2E-9E0F-4B27-B5AE-2B4706E55574}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="160">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -930,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7095CECD-B3C1-479B-A395-9B195FCE92D6}">
-  <dimension ref="A1:ES8"/>
+  <dimension ref="A1:ES11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="20" max="20" width="8.88671875" style="4"/>
@@ -3719,6 +3719,1353 @@
         <v>136.9653878</v>
       </c>
     </row>
+    <row r="9" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9">
+        <v>0.48</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0.48</v>
+      </c>
+      <c r="G9">
+        <v>0.02</v>
+      </c>
+      <c r="H9">
+        <v>0.02</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="L9">
+        <v>15296.24612</v>
+      </c>
+      <c r="M9">
+        <v>19370.285759999999</v>
+      </c>
+      <c r="N9">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="O9">
+        <v>10.71769387</v>
+      </c>
+      <c r="P9">
+        <v>4.0400000000000003E-6</v>
+      </c>
+      <c r="Q9">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="R9">
+        <v>251.61732309999999</v>
+      </c>
+      <c r="S9">
+        <v>180.586792</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0.590243085</v>
+      </c>
+      <c r="U9">
+        <v>250</v>
+      </c>
+      <c r="V9">
+        <v>500</v>
+      </c>
+      <c r="W9" s="4">
+        <v>250</v>
+      </c>
+      <c r="X9" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y9">
+        <v>500</v>
+      </c>
+      <c r="Z9">
+        <v>114.596</v>
+      </c>
+      <c r="AA9">
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AB9">
+        <v>96.084999999999994</v>
+      </c>
+      <c r="AC9">
+        <v>0.45542277199999998</v>
+      </c>
+      <c r="AD9">
+        <v>2.9943729999999998E-3</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF9">
+        <v>164</v>
+      </c>
+      <c r="AG9">
+        <v>52</v>
+      </c>
+      <c r="AH9">
+        <v>2000</v>
+      </c>
+      <c r="AI9">
+        <v>16.931000000000001</v>
+      </c>
+      <c r="AJ9">
+        <v>180.58799999999999</v>
+      </c>
+      <c r="AK9">
+        <v>3460.84</v>
+      </c>
+      <c r="AL9">
+        <v>5.48</v>
+      </c>
+      <c r="AM9">
+        <v>2.3149717509999999</v>
+      </c>
+      <c r="AN9">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="AO9">
+        <v>251.6</v>
+      </c>
+      <c r="AP9">
+        <v>108.6838316</v>
+      </c>
+      <c r="AQ9">
+        <v>285.01247999999998</v>
+      </c>
+      <c r="AR9">
+        <v>110.44</v>
+      </c>
+      <c r="AS9">
+        <v>384.57</v>
+      </c>
+      <c r="AT9">
+        <v>181.756</v>
+      </c>
+      <c r="AU9">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="AV9">
+        <v>78.028000000000006</v>
+      </c>
+      <c r="AW9">
+        <v>1.0228879660000001</v>
+      </c>
+      <c r="AX9">
+        <v>6.1456499999999997E-4</v>
+      </c>
+      <c r="AY9">
+        <v>249.3606667</v>
+      </c>
+      <c r="AZ9">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="BA9">
+        <v>1.9219999999999999</v>
+      </c>
+      <c r="BB9">
+        <v>143.96</v>
+      </c>
+      <c r="BC9">
+        <v>0.86109132799999999</v>
+      </c>
+      <c r="BD9">
+        <v>2.5713613999999999E-2</v>
+      </c>
+      <c r="BE9">
+        <v>4.8244129999999996E-3</v>
+      </c>
+      <c r="BF9">
+        <v>0.100737432</v>
+      </c>
+      <c r="BG9">
+        <v>2.1614299999999999E-4</v>
+      </c>
+      <c r="BH9">
+        <v>5.2086074000000003E-2</v>
+      </c>
+      <c r="BI9">
+        <v>0.453460048</v>
+      </c>
+      <c r="BJ9">
+        <v>2.4708790000000001E-2</v>
+      </c>
+      <c r="BK9">
+        <v>9.8234493000000006E-2</v>
+      </c>
+      <c r="BL9">
+        <v>0.22919963500000001</v>
+      </c>
+      <c r="BM9">
+        <v>1453.6841870000001</v>
+      </c>
+      <c r="BN9">
+        <v>0.476258615</v>
+      </c>
+      <c r="BO9">
+        <v>2.8367983109999999</v>
+      </c>
+      <c r="BP9">
+        <v>6.4197078000000005E-2</v>
+      </c>
+      <c r="BQ9">
+        <v>1382.2900990000001</v>
+      </c>
+      <c r="BR9">
+        <v>572.84799610000005</v>
+      </c>
+      <c r="BS9">
+        <v>1042.2361960000001</v>
+      </c>
+      <c r="BT9">
+        <v>468.82416499999999</v>
+      </c>
+      <c r="BU9">
+        <v>192.5912342</v>
+      </c>
+      <c r="BV9">
+        <v>208.91441850000001</v>
+      </c>
+      <c r="BW9">
+        <v>8.0015981E-2</v>
+      </c>
+      <c r="BX9">
+        <v>240.04794290000001</v>
+      </c>
+      <c r="BY9">
+        <v>223.431613</v>
+      </c>
+      <c r="BZ9" s="4">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="CA9">
+        <v>3358.7692830000001</v>
+      </c>
+      <c r="CB9">
+        <v>16.462475430000001</v>
+      </c>
+      <c r="CC9">
+        <v>46.271406540000001</v>
+      </c>
+      <c r="CD9">
+        <v>45.715451539999997</v>
+      </c>
+      <c r="CE9">
+        <v>2.1874442000000001E-2</v>
+      </c>
+      <c r="CF9" s="2">
+        <v>1.08381E-5</v>
+      </c>
+      <c r="CG9" s="2">
+        <v>1.10306E-6</v>
+      </c>
+      <c r="CH9">
+        <v>906572.58589999995</v>
+      </c>
+      <c r="CI9">
+        <v>15.296246119999999</v>
+      </c>
+      <c r="CJ9">
+        <v>45.438765080000003</v>
+      </c>
+      <c r="CK9" s="4">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="CL9">
+        <v>4.2106142999999999E-2</v>
+      </c>
+      <c r="CM9" s="2">
+        <v>6.17082E-6</v>
+      </c>
+      <c r="CN9" s="2">
+        <v>2.7980799999999998E-6</v>
+      </c>
+      <c r="CO9">
+        <v>357388.13919999998</v>
+      </c>
+      <c r="CP9">
+        <v>18.03892072</v>
+      </c>
+      <c r="CQ9">
+        <v>24.73414</v>
+      </c>
+      <c r="CR9">
+        <v>48.265258959999997</v>
+      </c>
+      <c r="CS9">
+        <v>2.0718836000000001E-2</v>
+      </c>
+      <c r="CT9" s="2">
+        <v>1.95356E-5</v>
+      </c>
+      <c r="CU9" s="2">
+        <v>3.2153999999999999E-9</v>
+      </c>
+      <c r="CV9">
+        <v>311003330.30000001</v>
+      </c>
+      <c r="CW9">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="CX9">
+        <v>33.403267239999998</v>
+      </c>
+      <c r="CY9">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="CZ9">
+        <v>2.1731309000000001E-2</v>
+      </c>
+      <c r="DA9" s="2">
+        <v>1.46722E-5</v>
+      </c>
+      <c r="DB9" s="2">
+        <v>7.5787200000000005E-7</v>
+      </c>
+      <c r="DC9">
+        <v>1319484.453</v>
+      </c>
+      <c r="DD9">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DE9">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DF9">
+        <v>49.317869760000001</v>
+      </c>
+      <c r="DG9">
+        <v>18.03892072</v>
+      </c>
+      <c r="DH9">
+        <v>180.5926</v>
+      </c>
+      <c r="DI9" s="2">
+        <v>1.00113E-5</v>
+      </c>
+      <c r="DJ9">
+        <v>0.94</v>
+      </c>
+      <c r="DK9">
+        <v>0.94</v>
+      </c>
+      <c r="DL9">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DM9">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DN9">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="DO9">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="DP9">
+        <v>180.5926</v>
+      </c>
+      <c r="DQ9" s="2">
+        <v>1.0650500000000001E-5</v>
+      </c>
+      <c r="DR9">
+        <v>1</v>
+      </c>
+      <c r="DS9">
+        <v>1</v>
+      </c>
+      <c r="DT9">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DU9">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DV9">
+        <v>45.715752180000003</v>
+      </c>
+      <c r="DW9">
+        <v>16.462982400000001</v>
+      </c>
+      <c r="DX9">
+        <v>180.5926</v>
+      </c>
+      <c r="DY9" s="2">
+        <v>1.0969600000000001E-5</v>
+      </c>
+      <c r="DZ9">
+        <v>1</v>
+      </c>
+      <c r="EA9">
+        <v>1</v>
+      </c>
+      <c r="EB9">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="EC9">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="ED9">
+        <v>23.75028618</v>
+      </c>
+      <c r="EE9">
+        <v>9.2622520000000003E-3</v>
+      </c>
+      <c r="EF9" s="2">
+        <v>6.0556999999999999E-7</v>
+      </c>
+      <c r="EG9">
+        <v>15.295102</v>
+      </c>
+      <c r="EH9" s="2">
+        <v>1.1807199999999999E-5</v>
+      </c>
+      <c r="EI9">
+        <v>2.253734219</v>
+      </c>
+      <c r="EJ9">
+        <v>47.055460930000002</v>
+      </c>
+      <c r="EK9" s="4">
+        <v>260.56978149999998</v>
+      </c>
+      <c r="EL9">
+        <v>256.22807749999998</v>
+      </c>
+      <c r="EM9" s="4">
+        <v>18038.920719999998</v>
+      </c>
+      <c r="EN9">
+        <v>16462.475429999999</v>
+      </c>
+      <c r="EO9">
+        <v>15296.24612</v>
+      </c>
+      <c r="EP9" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="EQ9" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER9" s="4">
+        <v>251.6173225</v>
+      </c>
+      <c r="ES9">
+        <v>136.9653878</v>
+      </c>
+    </row>
+    <row r="10" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10">
+        <v>0.48</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0.48</v>
+      </c>
+      <c r="G10">
+        <v>0.02</v>
+      </c>
+      <c r="H10">
+        <v>0.02</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="L10">
+        <v>15296.24612</v>
+      </c>
+      <c r="M10">
+        <v>19370.285759999999</v>
+      </c>
+      <c r="N10">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="O10">
+        <v>10.71769387</v>
+      </c>
+      <c r="P10">
+        <v>4.0400000000000003E-6</v>
+      </c>
+      <c r="Q10">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="R10">
+        <v>251.61732309999999</v>
+      </c>
+      <c r="S10">
+        <v>180.586792</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0.590243085</v>
+      </c>
+      <c r="U10">
+        <v>250</v>
+      </c>
+      <c r="V10">
+        <v>500</v>
+      </c>
+      <c r="W10" s="4">
+        <v>275</v>
+      </c>
+      <c r="X10" s="4">
+        <v>1.65</v>
+      </c>
+      <c r="Y10">
+        <v>500</v>
+      </c>
+      <c r="Z10">
+        <v>114.596</v>
+      </c>
+      <c r="AA10">
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AB10">
+        <v>96.084999999999994</v>
+      </c>
+      <c r="AC10">
+        <v>0.45542277199999998</v>
+      </c>
+      <c r="AD10">
+        <v>2.9943729999999998E-3</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF10">
+        <v>164</v>
+      </c>
+      <c r="AG10">
+        <v>52</v>
+      </c>
+      <c r="AH10">
+        <v>2000</v>
+      </c>
+      <c r="AI10">
+        <v>16.931000000000001</v>
+      </c>
+      <c r="AJ10">
+        <v>180.58799999999999</v>
+      </c>
+      <c r="AK10">
+        <v>3460.84</v>
+      </c>
+      <c r="AL10">
+        <v>5.48</v>
+      </c>
+      <c r="AM10">
+        <v>2.3149717509999999</v>
+      </c>
+      <c r="AN10">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="AO10">
+        <v>251.6</v>
+      </c>
+      <c r="AP10">
+        <v>108.6838316</v>
+      </c>
+      <c r="AQ10">
+        <v>285.01247999999998</v>
+      </c>
+      <c r="AR10">
+        <v>110.44</v>
+      </c>
+      <c r="AS10">
+        <v>384.57</v>
+      </c>
+      <c r="AT10">
+        <v>181.756</v>
+      </c>
+      <c r="AU10">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="AV10">
+        <v>78.028000000000006</v>
+      </c>
+      <c r="AW10">
+        <v>1.0228879660000001</v>
+      </c>
+      <c r="AX10">
+        <v>6.1456499999999997E-4</v>
+      </c>
+      <c r="AY10">
+        <v>249.3606667</v>
+      </c>
+      <c r="AZ10">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="BA10">
+        <v>1.9219999999999999</v>
+      </c>
+      <c r="BB10">
+        <v>143.96</v>
+      </c>
+      <c r="BC10">
+        <v>0.86109132799999999</v>
+      </c>
+      <c r="BD10">
+        <v>2.5713613999999999E-2</v>
+      </c>
+      <c r="BE10">
+        <v>4.8244129999999996E-3</v>
+      </c>
+      <c r="BF10">
+        <v>0.100737432</v>
+      </c>
+      <c r="BG10">
+        <v>2.1614299999999999E-4</v>
+      </c>
+      <c r="BH10">
+        <v>5.2086074000000003E-2</v>
+      </c>
+      <c r="BI10">
+        <v>0.453460048</v>
+      </c>
+      <c r="BJ10">
+        <v>2.4708790000000001E-2</v>
+      </c>
+      <c r="BK10">
+        <v>9.8234493000000006E-2</v>
+      </c>
+      <c r="BL10">
+        <v>0.22919963500000001</v>
+      </c>
+      <c r="BM10">
+        <v>1453.6841870000001</v>
+      </c>
+      <c r="BN10">
+        <v>0.476258615</v>
+      </c>
+      <c r="BO10">
+        <v>2.8367983109999999</v>
+      </c>
+      <c r="BP10">
+        <v>6.4197078000000005E-2</v>
+      </c>
+      <c r="BQ10">
+        <v>1382.2900990000001</v>
+      </c>
+      <c r="BR10">
+        <v>572.84799610000005</v>
+      </c>
+      <c r="BS10">
+        <v>1042.2361960000001</v>
+      </c>
+      <c r="BT10">
+        <v>468.82416499999999</v>
+      </c>
+      <c r="BU10">
+        <v>192.5912342</v>
+      </c>
+      <c r="BV10">
+        <v>208.91441850000001</v>
+      </c>
+      <c r="BW10">
+        <v>8.0015981E-2</v>
+      </c>
+      <c r="BX10">
+        <v>240.04794290000001</v>
+      </c>
+      <c r="BY10">
+        <v>223.431613</v>
+      </c>
+      <c r="BZ10" s="4">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="CA10">
+        <v>3358.7692830000001</v>
+      </c>
+      <c r="CB10">
+        <v>16.462475430000001</v>
+      </c>
+      <c r="CC10">
+        <v>46.271406540000001</v>
+      </c>
+      <c r="CD10">
+        <v>45.715451539999997</v>
+      </c>
+      <c r="CE10">
+        <v>2.1874442000000001E-2</v>
+      </c>
+      <c r="CF10" s="2">
+        <v>1.08E-5</v>
+      </c>
+      <c r="CG10" s="2">
+        <v>1.1000000000000001E-6</v>
+      </c>
+      <c r="CH10">
+        <v>906572.58589999995</v>
+      </c>
+      <c r="CI10">
+        <v>15.296246119999999</v>
+      </c>
+      <c r="CJ10">
+        <v>45.438765080000003</v>
+      </c>
+      <c r="CK10" s="4">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="CL10">
+        <v>4.2106142999999999E-2</v>
+      </c>
+      <c r="CM10" s="2">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="CN10" s="2">
+        <v>2.7999999999999999E-6</v>
+      </c>
+      <c r="CO10">
+        <v>357388.13919999998</v>
+      </c>
+      <c r="CP10">
+        <v>18.03892072</v>
+      </c>
+      <c r="CQ10">
+        <v>24.73414</v>
+      </c>
+      <c r="CR10">
+        <v>48.265258959999997</v>
+      </c>
+      <c r="CS10">
+        <v>2.0718836000000001E-2</v>
+      </c>
+      <c r="CT10" s="2">
+        <v>1.95E-5</v>
+      </c>
+      <c r="CU10" s="2">
+        <v>3.22E-9</v>
+      </c>
+      <c r="CV10">
+        <v>311003330.30000001</v>
+      </c>
+      <c r="CW10">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="CX10">
+        <v>33.403267239999998</v>
+      </c>
+      <c r="CY10">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="CZ10">
+        <v>2.1731309000000001E-2</v>
+      </c>
+      <c r="DA10" s="2">
+        <v>1.47E-5</v>
+      </c>
+      <c r="DB10" s="2">
+        <v>7.5799999999999998E-7</v>
+      </c>
+      <c r="DC10">
+        <v>1319484.453</v>
+      </c>
+      <c r="DD10">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DE10">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DF10">
+        <v>49.317869760000001</v>
+      </c>
+      <c r="DG10">
+        <v>18.03892072</v>
+      </c>
+      <c r="DH10">
+        <v>180.5926</v>
+      </c>
+      <c r="DI10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="DJ10">
+        <v>0.94</v>
+      </c>
+      <c r="DK10">
+        <v>0.94</v>
+      </c>
+      <c r="DL10">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DM10">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DN10">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="DO10">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="DP10">
+        <v>180.5926</v>
+      </c>
+      <c r="DQ10" s="2">
+        <v>1.0699999999999999E-5</v>
+      </c>
+      <c r="DR10">
+        <v>1</v>
+      </c>
+      <c r="DS10">
+        <v>1</v>
+      </c>
+      <c r="DT10">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DU10">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DV10">
+        <v>45.715752180000003</v>
+      </c>
+      <c r="DW10">
+        <v>16.462982400000001</v>
+      </c>
+      <c r="DX10">
+        <v>180.5926</v>
+      </c>
+      <c r="DY10" s="2">
+        <v>1.1E-5</v>
+      </c>
+      <c r="DZ10">
+        <v>1</v>
+      </c>
+      <c r="EA10">
+        <v>1</v>
+      </c>
+      <c r="EB10">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="EC10">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="ED10">
+        <v>23.75028618</v>
+      </c>
+      <c r="EE10">
+        <v>9.2622520000000003E-3</v>
+      </c>
+      <c r="EF10" s="2">
+        <v>6.06E-7</v>
+      </c>
+      <c r="EG10">
+        <v>15.295102</v>
+      </c>
+      <c r="EH10" s="2">
+        <v>1.1800000000000001E-5</v>
+      </c>
+      <c r="EI10">
+        <v>2.253734219</v>
+      </c>
+      <c r="EJ10">
+        <v>47.055460930000002</v>
+      </c>
+      <c r="EK10" s="4">
+        <v>260.56978149999998</v>
+      </c>
+      <c r="EL10">
+        <v>256.22807749999998</v>
+      </c>
+      <c r="EM10" s="4">
+        <v>18038.920719999998</v>
+      </c>
+      <c r="EN10">
+        <v>16462.475429999999</v>
+      </c>
+      <c r="EO10">
+        <v>15296.24612</v>
+      </c>
+      <c r="EP10" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="EQ10" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER10" s="4">
+        <v>251.6173225</v>
+      </c>
+      <c r="ES10">
+        <v>136.9653878</v>
+      </c>
+    </row>
+    <row r="11" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11">
+        <v>0.48</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0.48</v>
+      </c>
+      <c r="G11">
+        <v>0.02</v>
+      </c>
+      <c r="H11">
+        <v>0.02</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="L11">
+        <v>15296.24612</v>
+      </c>
+      <c r="M11">
+        <v>19370.285759999999</v>
+      </c>
+      <c r="N11">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="O11">
+        <v>10.71769387</v>
+      </c>
+      <c r="P11">
+        <v>4.0400000000000003E-6</v>
+      </c>
+      <c r="Q11">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="R11">
+        <v>251.61732309999999</v>
+      </c>
+      <c r="S11">
+        <v>180.586792</v>
+      </c>
+      <c r="T11" s="4">
+        <v>0.590243085</v>
+      </c>
+      <c r="U11">
+        <v>250</v>
+      </c>
+      <c r="V11">
+        <v>500</v>
+      </c>
+      <c r="W11" s="4">
+        <v>250</v>
+      </c>
+      <c r="X11" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="Y11">
+        <v>500</v>
+      </c>
+      <c r="Z11">
+        <v>114.596</v>
+      </c>
+      <c r="AA11">
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AB11">
+        <v>96.084999999999994</v>
+      </c>
+      <c r="AC11">
+        <v>0.45542277199999998</v>
+      </c>
+      <c r="AD11">
+        <v>2.9943729999999998E-3</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF11">
+        <v>164</v>
+      </c>
+      <c r="AG11">
+        <v>52</v>
+      </c>
+      <c r="AH11">
+        <v>2000</v>
+      </c>
+      <c r="AI11">
+        <v>16.931000000000001</v>
+      </c>
+      <c r="AJ11">
+        <v>180.58799999999999</v>
+      </c>
+      <c r="AK11">
+        <v>3460.84</v>
+      </c>
+      <c r="AL11">
+        <v>5.48</v>
+      </c>
+      <c r="AM11">
+        <v>2.3149717509999999</v>
+      </c>
+      <c r="AN11">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="AO11">
+        <v>251.6</v>
+      </c>
+      <c r="AP11">
+        <v>108.6838316</v>
+      </c>
+      <c r="AQ11">
+        <v>285.01247999999998</v>
+      </c>
+      <c r="AR11">
+        <v>110.44</v>
+      </c>
+      <c r="AS11">
+        <v>384.57</v>
+      </c>
+      <c r="AT11">
+        <v>181.756</v>
+      </c>
+      <c r="AU11">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="AV11">
+        <v>78.028000000000006</v>
+      </c>
+      <c r="AW11">
+        <v>1.0228879660000001</v>
+      </c>
+      <c r="AX11">
+        <v>6.1456499999999997E-4</v>
+      </c>
+      <c r="AY11">
+        <v>249.3606667</v>
+      </c>
+      <c r="AZ11">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="BA11">
+        <v>1.9219999999999999</v>
+      </c>
+      <c r="BB11">
+        <v>143.96</v>
+      </c>
+      <c r="BC11">
+        <v>0.86109132799999999</v>
+      </c>
+      <c r="BD11">
+        <v>2.5713613999999999E-2</v>
+      </c>
+      <c r="BE11">
+        <v>4.8244129999999996E-3</v>
+      </c>
+      <c r="BF11">
+        <v>0.100737432</v>
+      </c>
+      <c r="BG11">
+        <v>2.1614299999999999E-4</v>
+      </c>
+      <c r="BH11">
+        <v>5.2086074000000003E-2</v>
+      </c>
+      <c r="BI11">
+        <v>0.453460048</v>
+      </c>
+      <c r="BJ11">
+        <v>2.4708790000000001E-2</v>
+      </c>
+      <c r="BK11">
+        <v>9.8234493000000006E-2</v>
+      </c>
+      <c r="BL11">
+        <v>0.22919963500000001</v>
+      </c>
+      <c r="BM11">
+        <v>1453.6841870000001</v>
+      </c>
+      <c r="BN11">
+        <v>0.476258615</v>
+      </c>
+      <c r="BO11">
+        <v>2.8367983109999999</v>
+      </c>
+      <c r="BP11">
+        <v>6.4197078000000005E-2</v>
+      </c>
+      <c r="BQ11">
+        <v>1382.2900990000001</v>
+      </c>
+      <c r="BR11">
+        <v>572.84799610000005</v>
+      </c>
+      <c r="BS11">
+        <v>1042.2361960000001</v>
+      </c>
+      <c r="BT11">
+        <v>468.82416499999999</v>
+      </c>
+      <c r="BU11">
+        <v>192.5912342</v>
+      </c>
+      <c r="BV11">
+        <v>208.91441850000001</v>
+      </c>
+      <c r="BW11">
+        <v>8.0015981E-2</v>
+      </c>
+      <c r="BX11">
+        <v>240.04794290000001</v>
+      </c>
+      <c r="BY11">
+        <v>223.431613</v>
+      </c>
+      <c r="BZ11" s="4">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="CA11">
+        <v>3358.7692830000001</v>
+      </c>
+      <c r="CB11">
+        <v>16.462475430000001</v>
+      </c>
+      <c r="CC11">
+        <v>46.271406540000001</v>
+      </c>
+      <c r="CD11">
+        <v>45.715451539999997</v>
+      </c>
+      <c r="CE11">
+        <v>2.1874442000000001E-2</v>
+      </c>
+      <c r="CF11" s="2">
+        <v>1.08E-5</v>
+      </c>
+      <c r="CG11" s="2">
+        <v>1.1000000000000001E-6</v>
+      </c>
+      <c r="CH11">
+        <v>906572.58589999995</v>
+      </c>
+      <c r="CI11">
+        <v>15.296246119999999</v>
+      </c>
+      <c r="CJ11">
+        <v>45.438765080000003</v>
+      </c>
+      <c r="CK11" s="4">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="CL11">
+        <v>4.2106142999999999E-2</v>
+      </c>
+      <c r="CM11" s="2">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="CN11" s="2">
+        <v>2.7999999999999999E-6</v>
+      </c>
+      <c r="CO11">
+        <v>357388.13919999998</v>
+      </c>
+      <c r="CP11">
+        <v>18.03892072</v>
+      </c>
+      <c r="CQ11">
+        <v>24.73414</v>
+      </c>
+      <c r="CR11">
+        <v>48.265258959999997</v>
+      </c>
+      <c r="CS11">
+        <v>2.0718836000000001E-2</v>
+      </c>
+      <c r="CT11" s="2">
+        <v>1.95E-5</v>
+      </c>
+      <c r="CU11" s="2">
+        <v>3.22E-9</v>
+      </c>
+      <c r="CV11">
+        <v>311003330.30000001</v>
+      </c>
+      <c r="CW11">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="CX11">
+        <v>33.403267239999998</v>
+      </c>
+      <c r="CY11">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="CZ11">
+        <v>2.1731309000000001E-2</v>
+      </c>
+      <c r="DA11" s="2">
+        <v>1.47E-5</v>
+      </c>
+      <c r="DB11" s="2">
+        <v>7.5799999999999998E-7</v>
+      </c>
+      <c r="DC11">
+        <v>1319484.453</v>
+      </c>
+      <c r="DD11">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DE11">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DF11">
+        <v>49.317869760000001</v>
+      </c>
+      <c r="DG11">
+        <v>18.03892072</v>
+      </c>
+      <c r="DH11">
+        <v>180.5926</v>
+      </c>
+      <c r="DI11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="DJ11">
+        <v>0.94</v>
+      </c>
+      <c r="DK11">
+        <v>0.94</v>
+      </c>
+      <c r="DL11">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DM11">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DN11">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="DO11">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="DP11">
+        <v>180.5926</v>
+      </c>
+      <c r="DQ11" s="2">
+        <v>1.0699999999999999E-5</v>
+      </c>
+      <c r="DR11">
+        <v>1</v>
+      </c>
+      <c r="DS11">
+        <v>1</v>
+      </c>
+      <c r="DT11">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DU11">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DV11">
+        <v>45.715752180000003</v>
+      </c>
+      <c r="DW11">
+        <v>16.462982400000001</v>
+      </c>
+      <c r="DX11">
+        <v>180.5926</v>
+      </c>
+      <c r="DY11" s="2">
+        <v>1.1E-5</v>
+      </c>
+      <c r="DZ11">
+        <v>1</v>
+      </c>
+      <c r="EA11">
+        <v>1</v>
+      </c>
+      <c r="EB11">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="EC11">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="ED11">
+        <v>23.75028618</v>
+      </c>
+      <c r="EE11">
+        <v>9.2622520000000003E-3</v>
+      </c>
+      <c r="EF11" s="2">
+        <v>6.06E-7</v>
+      </c>
+      <c r="EG11">
+        <v>15.295102</v>
+      </c>
+      <c r="EH11" s="2">
+        <v>1.1800000000000001E-5</v>
+      </c>
+      <c r="EI11">
+        <v>2.253734219</v>
+      </c>
+      <c r="EJ11">
+        <v>47.055460930000002</v>
+      </c>
+      <c r="EK11" s="4">
+        <v>260.56978149999998</v>
+      </c>
+      <c r="EL11">
+        <v>256.22807749999998</v>
+      </c>
+      <c r="EM11" s="4">
+        <v>18038.920719999998</v>
+      </c>
+      <c r="EN11">
+        <v>16462.475429999999</v>
+      </c>
+      <c r="EO11">
+        <v>15296.24612</v>
+      </c>
+      <c r="EP11" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="EQ11" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER11" s="4">
+        <v>260.56978149999998</v>
+      </c>
+      <c r="ES11">
+        <v>136.9653878</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/et_custom_input_data.xlsx
+++ b/et_custom_input_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\ETtoKGT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B474354C-AF7A-4285-A46A-6BD9654C5A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AF5F7C-C7E4-4C8B-9A41-BF0110A1F815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D50FBC2E-9E0F-4B27-B5AE-2B4706E55574}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="160">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -540,7 +540,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,8 +553,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -577,11 +583,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -591,6 +612,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7095CECD-B3C1-479B-A395-9B195FCE92D6}">
-  <dimension ref="A1:ES11"/>
+  <dimension ref="A1:ES12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="20" max="20" width="8.88671875" style="4"/>
@@ -5066,6 +5090,455 @@
         <v>136.9653878</v>
       </c>
     </row>
+    <row r="12" spans="1:149" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12">
+        <v>0.48</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0.48</v>
+      </c>
+      <c r="G12">
+        <v>0.02</v>
+      </c>
+      <c r="H12">
+        <v>0.02</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>3454.8464669999998</v>
+      </c>
+      <c r="L12">
+        <v>15296.24612</v>
+      </c>
+      <c r="M12">
+        <v>19370.285759999999</v>
+      </c>
+      <c r="N12">
+        <v>23.749503539999999</v>
+      </c>
+      <c r="O12">
+        <v>10.71769387</v>
+      </c>
+      <c r="P12">
+        <v>4.0400000000000003E-6</v>
+      </c>
+      <c r="Q12">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="R12">
+        <v>251.61732309999999</v>
+      </c>
+      <c r="S12">
+        <v>180.586792</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0.590243085</v>
+      </c>
+      <c r="U12">
+        <v>250</v>
+      </c>
+      <c r="V12">
+        <v>500</v>
+      </c>
+      <c r="W12" s="4">
+        <v>250</v>
+      </c>
+      <c r="X12" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="Y12">
+        <v>500</v>
+      </c>
+      <c r="Z12">
+        <v>114.596</v>
+      </c>
+      <c r="AA12">
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AB12">
+        <v>96.084999999999994</v>
+      </c>
+      <c r="AC12">
+        <v>0.45542277199999998</v>
+      </c>
+      <c r="AD12">
+        <v>2.9943729999999998E-3</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF12">
+        <v>164</v>
+      </c>
+      <c r="AG12">
+        <v>52</v>
+      </c>
+      <c r="AH12">
+        <v>2000</v>
+      </c>
+      <c r="AI12">
+        <v>16.931000000000001</v>
+      </c>
+      <c r="AJ12">
+        <v>180.58799999999999</v>
+      </c>
+      <c r="AK12">
+        <v>3460.84</v>
+      </c>
+      <c r="AL12">
+        <v>5.48</v>
+      </c>
+      <c r="AM12">
+        <v>2.3149717509999999</v>
+      </c>
+      <c r="AN12">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="AO12">
+        <v>251.6</v>
+      </c>
+      <c r="AP12">
+        <v>108.6838316</v>
+      </c>
+      <c r="AQ12">
+        <v>285.01247999999998</v>
+      </c>
+      <c r="AR12">
+        <v>110.44</v>
+      </c>
+      <c r="AS12">
+        <v>384.57</v>
+      </c>
+      <c r="AT12">
+        <v>181.756</v>
+      </c>
+      <c r="AU12">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="AV12">
+        <v>78.028000000000006</v>
+      </c>
+      <c r="AW12">
+        <v>1.0228879660000001</v>
+      </c>
+      <c r="AX12">
+        <v>6.1456499999999997E-4</v>
+      </c>
+      <c r="AY12">
+        <v>249.3606667</v>
+      </c>
+      <c r="AZ12">
+        <v>103.72799999999999</v>
+      </c>
+      <c r="BA12">
+        <v>1.9219999999999999</v>
+      </c>
+      <c r="BB12">
+        <v>143.96</v>
+      </c>
+      <c r="BC12">
+        <v>0.86109132799999999</v>
+      </c>
+      <c r="BD12">
+        <v>2.5713613999999999E-2</v>
+      </c>
+      <c r="BE12">
+        <v>4.8244129999999996E-3</v>
+      </c>
+      <c r="BF12">
+        <v>0.100737432</v>
+      </c>
+      <c r="BG12">
+        <v>2.1614299999999999E-4</v>
+      </c>
+      <c r="BH12">
+        <v>5.2086074000000003E-2</v>
+      </c>
+      <c r="BI12">
+        <v>0.453460048</v>
+      </c>
+      <c r="BJ12">
+        <v>2.4708790000000001E-2</v>
+      </c>
+      <c r="BK12">
+        <v>9.8234493000000006E-2</v>
+      </c>
+      <c r="BL12">
+        <v>0.22919963500000001</v>
+      </c>
+      <c r="BM12">
+        <v>1453.6841870000001</v>
+      </c>
+      <c r="BN12">
+        <v>0.476258615</v>
+      </c>
+      <c r="BO12">
+        <v>2.8367983109999999</v>
+      </c>
+      <c r="BP12">
+        <v>6.4197078000000005E-2</v>
+      </c>
+      <c r="BQ12">
+        <v>1382.2900990000001</v>
+      </c>
+      <c r="BR12">
+        <v>572.84799610000005</v>
+      </c>
+      <c r="BS12">
+        <v>1042.2361960000001</v>
+      </c>
+      <c r="BT12">
+        <v>468.82416499999999</v>
+      </c>
+      <c r="BU12">
+        <v>192.5912342</v>
+      </c>
+      <c r="BV12">
+        <v>208.91441850000001</v>
+      </c>
+      <c r="BW12">
+        <v>8.0015981E-2</v>
+      </c>
+      <c r="BX12">
+        <v>240.04794290000001</v>
+      </c>
+      <c r="BY12">
+        <v>223.431613</v>
+      </c>
+      <c r="BZ12" s="5">
+        <v>3454.8464667112039</v>
+      </c>
+      <c r="CA12">
+        <v>3358.7692830000001</v>
+      </c>
+      <c r="CB12">
+        <v>16.462475430000001</v>
+      </c>
+      <c r="CC12">
+        <v>46.271406540000001</v>
+      </c>
+      <c r="CD12">
+        <v>45.715451539999997</v>
+      </c>
+      <c r="CE12">
+        <v>2.1874442000000001E-2</v>
+      </c>
+      <c r="CF12" s="2">
+        <v>1.08E-5</v>
+      </c>
+      <c r="CG12" s="2">
+        <v>1.1000000000000001E-6</v>
+      </c>
+      <c r="CH12">
+        <v>906572.58589999995</v>
+      </c>
+      <c r="CI12">
+        <v>15.296246119999999</v>
+      </c>
+      <c r="CJ12">
+        <v>45.438765080000003</v>
+      </c>
+      <c r="CK12" s="5">
+        <v>36.272170000000003</v>
+      </c>
+      <c r="CL12">
+        <v>4.2106142999999999E-2</v>
+      </c>
+      <c r="CM12" s="2">
+        <v>6.1700000000000002E-6</v>
+      </c>
+      <c r="CN12" s="2">
+        <v>2.7999999999999999E-6</v>
+      </c>
+      <c r="CO12">
+        <v>357388.13919999998</v>
+      </c>
+      <c r="CP12">
+        <v>18.03892072</v>
+      </c>
+      <c r="CQ12">
+        <v>24.73414</v>
+      </c>
+      <c r="CR12">
+        <v>48.265258959999997</v>
+      </c>
+      <c r="CS12">
+        <v>2.0718836000000001E-2</v>
+      </c>
+      <c r="CT12" s="2">
+        <v>1.95E-5</v>
+      </c>
+      <c r="CU12" s="2">
+        <v>3.22E-9</v>
+      </c>
+      <c r="CV12">
+        <v>311003330.30000001</v>
+      </c>
+      <c r="CW12">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="CX12">
+        <v>33.403267239999998</v>
+      </c>
+      <c r="CY12">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="CZ12">
+        <v>2.1731309000000001E-2</v>
+      </c>
+      <c r="DA12" s="2">
+        <v>1.47E-5</v>
+      </c>
+      <c r="DB12" s="2">
+        <v>7.5799999999999998E-7</v>
+      </c>
+      <c r="DC12">
+        <v>1319484.453</v>
+      </c>
+      <c r="DD12">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DE12">
+        <v>-7733.9118230000004</v>
+      </c>
+      <c r="DF12">
+        <v>49.317869760000001</v>
+      </c>
+      <c r="DG12">
+        <v>18.03892072</v>
+      </c>
+      <c r="DH12">
+        <v>180.5926</v>
+      </c>
+      <c r="DI12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="DJ12">
+        <v>0.94</v>
+      </c>
+      <c r="DK12">
+        <v>0.94</v>
+      </c>
+      <c r="DL12">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DM12">
+        <v>50781.434370000003</v>
+      </c>
+      <c r="DN12">
+        <v>46.016555449999998</v>
+      </c>
+      <c r="DO12">
+        <v>16.956278170000001</v>
+      </c>
+      <c r="DP12">
+        <v>180.5926</v>
+      </c>
+      <c r="DQ12" s="2">
+        <v>1.0699999999999999E-5</v>
+      </c>
+      <c r="DR12">
+        <v>1</v>
+      </c>
+      <c r="DS12">
+        <v>1</v>
+      </c>
+      <c r="DT12">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DU12">
+        <v>93128.501780000006</v>
+      </c>
+      <c r="DV12">
+        <v>45.715752180000003</v>
+      </c>
+      <c r="DW12">
+        <v>16.462982400000001</v>
+      </c>
+      <c r="DX12">
+        <v>180.5926</v>
+      </c>
+      <c r="DY12" s="2">
+        <v>1.1E-5</v>
+      </c>
+      <c r="DZ12">
+        <v>1</v>
+      </c>
+      <c r="EA12">
+        <v>1</v>
+      </c>
+      <c r="EB12">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="EC12">
+        <v>140812.95379999999</v>
+      </c>
+      <c r="ED12">
+        <v>23.75028618</v>
+      </c>
+      <c r="EE12">
+        <v>9.2622520000000003E-3</v>
+      </c>
+      <c r="EF12" s="2">
+        <v>6.06E-7</v>
+      </c>
+      <c r="EG12">
+        <v>15.295102</v>
+      </c>
+      <c r="EH12" s="2">
+        <v>1.1800000000000001E-5</v>
+      </c>
+      <c r="EI12">
+        <v>2.253734219</v>
+      </c>
+      <c r="EJ12">
+        <v>47.055460930000002</v>
+      </c>
+      <c r="EK12" s="4">
+        <v>260.56978149999998</v>
+      </c>
+      <c r="EL12">
+        <v>256.22807749999998</v>
+      </c>
+      <c r="EM12" s="5">
+        <v>18038.934929999999</v>
+      </c>
+      <c r="EN12">
+        <v>16462.475429999999</v>
+      </c>
+      <c r="EO12">
+        <v>15296.24612</v>
+      </c>
+      <c r="EP12" s="4">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="EQ12" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER12" s="5">
+        <v>264.16541693165289</v>
+      </c>
+      <c r="ES12">
+        <v>136.9653878</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
